--- a/iivw/demo/iivw_results.xlsx
+++ b/iivw/demo/iivw_results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="144" uniqueCount="33">
   <si>
     <t>IIW vs FIPTIW: Cognitive Score</t>
   </si>
@@ -118,10 +118,1468 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="338">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="675">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1590,7 +3048,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="253">
+  <borders count="505">
     <border>
       <left/>
       <right/>
@@ -3314,11 +4772,1727 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="505">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -4301,6 +7475,990 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="337" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="257" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="259" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="260" xfId="0"/>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="668" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="670" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4316,246 +8474,246 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" style="2" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="3" customWidth="true"/>
-    <col min="6" max="6" width="5.11328125" style="4" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="5" customWidth="true"/>
-    <col min="7" max="7" width="11.11328125" style="6" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="7" customWidth="true"/>
-    <col min="8" max="8" width="7.7109375" style="8" customWidth="true"/>
+    <col min="2" max="2" width="31.7109375" style="254" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="255" customWidth="true"/>
+    <col min="6" max="6" width="5.11328125" style="256" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="257" customWidth="true"/>
+    <col min="7" max="7" width="11.11328125" style="258" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="259" customWidth="true"/>
+    <col min="8" max="8" width="7.7109375" style="260" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="181" t="s">
+    <row r="1" s="253" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="433" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="182" t="s">
+      <c r="B1" s="434" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="183" t="s">
+      <c r="C1" s="435" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="184" t="s">
+      <c r="D1" s="436" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="185" t="s">
+      <c r="E1" s="437" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="186" t="s">
+      <c r="F1" s="438" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="187" t="s">
+      <c r="G1" s="439" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="188" t="s">
+      <c r="H1" s="440" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="441" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="190" t="s">
+      <c r="B2" s="442" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="443" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="192" t="s">
+      <c r="D2" s="444" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="193" t="s">
+      <c r="E2" s="445" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="194" t="s">
+      <c r="F2" s="446" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="195" t="s">
+      <c r="G2" s="447" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="196" t="s">
+      <c r="H2" s="448" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="197" t="s">
+      <c r="A3" s="449" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="450" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="199" t="s">
+      <c r="C3" s="451" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="200" t="s">
+      <c r="D3" s="452" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="201" t="s">
+      <c r="E3" s="453" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="202" t="s">
+      <c r="F3" s="454" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="203" t="s">
+      <c r="G3" s="455" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="204" t="s">
+      <c r="H3" s="456" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="205" t="s">
+      <c r="A4" s="457" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="206" t="s">
+      <c r="B4" s="458" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="459" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="460" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="461" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="210" t="s">
+      <c r="F4" s="462" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="211" t="s">
+      <c r="G4" s="463" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="212" t="s">
+      <c r="H4" s="464" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="213" t="s">
+      <c r="A5" s="465" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="466" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="215" t="s">
+      <c r="C5" s="467" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="216" t="s">
+      <c r="D5" s="468" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="217" t="s">
+      <c r="E5" s="469" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="218" t="s">
+      <c r="F5" s="470" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="219" t="s">
+      <c r="G5" s="471" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="220" t="s">
+      <c r="H5" s="472" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="221" t="s">
+      <c r="A6" s="473" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="222" t="s">
+      <c r="B6" s="474" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="223" t="s">
+      <c r="C6" s="475" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="224" t="s">
+      <c r="D6" s="476" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="225" t="s">
+      <c r="E6" s="477" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="226" t="s">
+      <c r="F6" s="478" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="227" t="s">
+      <c r="G6" s="479" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="228" t="s">
+      <c r="H6" s="480" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="229" t="s">
+      <c r="A7" s="481" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="230" t="s">
+      <c r="B7" s="482" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="231" t="s">
+      <c r="C7" s="483" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="232" t="s">
+      <c r="D7" s="484" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="233" t="s">
+      <c r="E7" s="485" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="234" t="s">
+      <c r="F7" s="486" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="235" t="s">
+      <c r="G7" s="487" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="236" t="s">
+      <c r="H7" s="488" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="237" t="s">
+      <c r="A8" s="489" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="238" t="s">
+      <c r="B8" s="490" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="239" t="s">
+      <c r="C8" s="491" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="240" t="s">
+      <c r="D8" s="492" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="241" t="s">
+      <c r="E8" s="493" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="242" t="s">
+      <c r="F8" s="494" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="243" t="s">
+      <c r="G8" s="495" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="244" t="s">
+      <c r="H8" s="496" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="245" t="s">
+      <c r="A9" s="497" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="246" t="s">
+      <c r="B9" s="498" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="247" t="s">
+      <c r="C9" s="499" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="248" t="s">
+      <c r="D9" s="500" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="249" t="s">
+      <c r="E9" s="501" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="250" t="s">
+      <c r="F9" s="502" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="251" t="s">
+      <c r="G9" s="503" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="252" t="s">
+      <c r="H9" s="504" t="s">
         <v>1</v>
       </c>
     </row>

--- a/iivw/demo/iivw_results.xlsx
+++ b/iivw/demo/iivw_results.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Diagnostic" sheetId="1" r:id="rId2"/>
+    <sheet name="Visit waves" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="176" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="271" uniqueCount="138">
   <si>
     <t>IIVW diagnostic model comparison</t>
   </si>
@@ -305,12 +306,135 @@
   <si>
     <t>0.24</t>
   </si>
+  <si>
+    <t>Treatment by visit wave</t>
+  </si>
+  <si>
+    <t>NTZ-like (vs. RTX-like)</t>
+  </si>
+  <si>
+    <t>Visit wave: Month 6 (vs. Baseline)</t>
+  </si>
+  <si>
+    <t>Visit wave: Month 12 (vs. Baseline)</t>
+  </si>
+  <si>
+    <t>Visit wave: Month 18 (vs. Baseline)</t>
+  </si>
+  <si>
+    <t>NTZ-like x Visit wave: Month 6</t>
+  </si>
+  <si>
+    <t>NTZ-like x Visit wave: Month 12</t>
+  </si>
+  <si>
+    <t>NTZ-like x Visit wave: Month 18</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>-0.03</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>1.56</t>
+  </si>
+  <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <t>-0.12</t>
+  </si>
+  <si>
+    <t>-0.09</t>
+  </si>
+  <si>
+    <t>2.91</t>
+  </si>
+  <si>
+    <t>1,243</t>
+  </si>
+  <si>
+    <t>(-0.17, 0.91)</t>
+  </si>
+  <si>
+    <t>(-0.31, 0.25)</t>
+  </si>
+  <si>
+    <t>(-0.35, -0.05)</t>
+  </si>
+  <si>
+    <t>(-0.06, 0.03)</t>
+  </si>
+  <si>
+    <t>(-0.25, 0.32)</t>
+  </si>
+  <si>
+    <t>(-0.47, 0.24)</t>
+  </si>
+  <si>
+    <t>(0.49, 1.56)</t>
+  </si>
+  <si>
+    <t>(1.02, 2.11)</t>
+  </si>
+  <si>
+    <t>(1.58, 2.66)</t>
+  </si>
+  <si>
+    <t>(-0.88, 0.64)</t>
+  </si>
+  <si>
+    <t>(-0.81, 0.63)</t>
+  </si>
+  <si>
+    <t>(-0.39, 1.12)</t>
+  </si>
+  <si>
+    <t>(1.29, 4.53)</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="719">
+  <fonts count="1094">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -2953,6 +3077,1534 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
       <name val="Arial"/>
     </font>
     <font>
@@ -3264,7 +4916,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="530">
+  <borders count="805">
     <border>
       <left/>
       <right/>
@@ -6903,11 +8555,1900 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="530">
+  <cellXfs count="805">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -8986,6 +12527,1088 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="718" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="530" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="531" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="532" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="533" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="534" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="535" xfId="0"/>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="722" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="724" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="726" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="728" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="730" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="732" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="734" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="736" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="746" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="820" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="822" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="824" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="826" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="828" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="844" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="846" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="848" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="850" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="852" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="858" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="860" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="862" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="864" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="866" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="876" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="878" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="880" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="882" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="884" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="886" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="890" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="900" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="902" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="916" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="965" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="967" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="991" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="993" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="995" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="997" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1080" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1089" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1091" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1093" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9585,4 +14208,348 @@
     <mergeCell ref="I16:K16"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="531" customWidth="true"/>
+    <col min="2" max="2" width="36.7109375" style="532" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="533" customWidth="true"/>
+    <col min="4" max="4" width="14.2109375" style="534" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="535" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="530" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="639" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="631" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="631" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="631" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="631" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="541" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="728" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="678" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="679" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="692" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="546" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="729" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="685" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="686" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="693" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="551" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="730" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="757" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="758" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="759" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="556" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="731" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="760" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="761" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="762" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="561" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="732" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="763" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="764" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="765" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="566" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="733" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="766" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="767" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="768" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="571" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="734" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="769" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="770" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="771" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="576" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="735" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="772" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="773" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="774" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="581" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="736" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="775" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="776" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="777" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="586" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="737" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="778" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="779" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="780" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="591" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="738" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="781" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="782" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="783" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="596" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="739" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="784" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="785" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="786" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="601" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="740" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="787" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="788" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="789" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="606" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="741" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="790" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="791" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="792" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="611" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="742" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="793" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="794" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="795" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="616" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="743" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="796" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="797" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="798" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="621" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="744" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="799" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="800" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="801" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="626" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="750" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="802" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="803" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="804" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C19:E19"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/iivw/demo/iivw_results.xlsx
+++ b/iivw/demo/iivw_results.xlsx
@@ -434,7 +434,111 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1094">
+  <fonts count="1152">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3378,6 +3482,134 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4916,7 +5148,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="805">
+  <borders count="863">
     <border>
       <left/>
       <right/>
@@ -6513,6 +6745,188 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -9403,6 +9817,230 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -10448,7 +11086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="805">
+  <cellXfs count="863">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -10462,1156 +11100,1156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="188" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="226" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="248" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="292" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="302" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="304" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="316" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="324" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="330" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="332" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="338" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="340" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="342" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="346" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="352" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="356" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="358" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="360" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="364" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="366" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="368" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="374" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="375" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="376" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="377" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="379" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="381" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="383" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="385" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="387" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="389" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="391" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="393" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="395" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="397" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="399" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="400" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="401" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="402" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="403" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="404" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="405" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="406" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="407" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="408" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="409" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="410" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="411" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="412" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="413" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="414" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="415" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="416" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="417" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="418" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="419" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="420" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="421" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="423" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="424" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="425" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="426" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="427" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="428" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="429" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="430" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="431" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="432" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="433" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="434" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="435" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="436" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="437" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="438" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="439" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="440" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="441" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="443" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="444" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="446" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="447" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="448" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="449" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="450" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="451" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="452" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="453" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="454" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="455" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="456" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="457" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="458" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="459" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="460" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="461" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="463" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="464" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="465" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="466" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="467" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="468" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="469" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="470" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="471" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="472" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="473" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="474" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="475" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="476" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="477" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="478" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="479" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="480" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="481" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="482" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="483" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="484" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="485" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="486" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="487" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="488" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="489" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="490" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11623,151 +12261,151 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="492" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="493" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="494" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="495" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="496" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="497" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="498" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="499" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="500" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="501" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="502" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="503" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="504" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="505" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="506" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="507" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="508" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="509" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="510" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="511" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="512" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="513" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="514" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="515" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="516" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="517" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="518" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="519" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="520" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="521" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="522" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="523" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="524" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="525" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="526" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="527" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="528" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="529" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11775,109 +12413,109 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="530" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="531" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="532" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="533" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="534" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="535" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="536" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="537" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="538" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="539" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="540" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="541" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="542" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="543" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="544" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="556" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -11891,103 +12529,103 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="559" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="561" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="563" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="567" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="569" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="571" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="572" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="573" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="574" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="575" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="576" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="577" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="578" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="579" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="580" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="581" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="582" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="583" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="584" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11995,175 +12633,175 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="585" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="586" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="587" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="588" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="589" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="590" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="591" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="592" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="593" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="594" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="595" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="597" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="598" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="599" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="600" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="601" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="602" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="603" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="604" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="605" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="606" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="608" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="610" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="612" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="614" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="617" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="618" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="620" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="621" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="623" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="624" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="625" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="626" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="627" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="628" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -12495,1120 +13133,1352 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="710" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="712" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="714" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="716" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="718" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="722" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="724" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="726" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="728" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="730" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="732" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="734" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="736" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="711" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="712" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="713" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="714" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="715" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="716" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="717" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="718" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="530" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="531" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="532" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="533" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="534" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="535" xfId="0"/>
-    <xf numFmtId="0" fontId="720" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="722" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="724" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="726" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="728" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="730" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="732" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="734" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="736" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="738" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="740" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="742" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="744" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="746" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="748" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="750" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="752" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="754" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="756" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="758" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="760" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="762" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="764" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="766" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="768" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="770" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="772" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="774" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="776" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="778" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="780" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="782" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="784" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="786" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="788" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="790" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="792" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="794" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="796" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="798" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="800" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="804" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="806" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="810" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="812" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="814" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="816" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="818" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="820" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="822" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="824" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="826" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="828" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="830" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="832" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="834" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="836" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="838" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="840" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="842" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="844" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="846" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="848" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="850" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="852" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="854" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="856" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="858" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="860" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="862" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="864" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="866" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="868" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="870" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="872" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="874" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="876" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="878" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="880" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="882" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="884" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="886" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="888" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="890" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="892" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="894" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="896" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="898" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="900" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="902" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="904" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="906" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="908" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="910" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="912" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="914" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="916" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="918" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="919" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="556" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="557" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="558" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="559" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="560" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="561" xfId="0"/>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="920" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="746" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="820" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="822" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="824" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="826" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="828" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="844" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="846" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="848" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="850" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="852" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="858" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="860" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="862" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="864" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="866" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="876" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="878" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="880" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="882" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="884" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="886" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="890" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="900" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="902" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="916" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="921" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="923" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="925" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="927" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="929" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="931" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="932" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="933" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="934" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="935" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="936" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="991" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="993" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="937" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="995" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="938" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="939" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="997" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="940" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="941" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="943" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="944" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="945" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="946" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="947" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="948" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="949" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="950" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="951" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="952" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="953" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="954" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="955" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="956" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="957" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="958" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="959" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="960" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="961" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="962" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="963" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="964" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="965" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="966" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="967" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="968" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="969" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="970" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="971" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="972" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="973" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="974" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="975" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="976" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="977" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="978" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="979" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="980" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="981" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="982" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="983" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="984" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="985" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="986" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="987" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="988" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="989" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="990" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="991" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="992" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="993" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="994" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="995" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="996" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="997" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="998" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="999" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1000" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1001" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1002" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1003" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1004" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1005" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1006" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1007" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1008" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1009" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1010" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1011" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1012" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1013" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1014" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1015" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1016" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1017" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1018" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1019" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1020" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1021" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1022" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1023" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1024" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1025" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1026" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1027" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1028" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1029" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1030" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1031" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1032" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1033" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1034" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1035" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1036" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1037" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1038" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1039" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1040" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1041" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1042" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1043" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1044" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1080" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1089" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1091" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1093" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1094" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1095" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1096" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1097" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1098" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1099" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1100" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1101" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1102" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1045" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1046" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1047" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1048" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1049" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1050" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1051" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1052" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1053" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1054" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1055" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1056" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1057" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1058" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1059" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1060" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1061" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1062" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1063" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1064" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1065" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1066" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1067" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1068" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1069" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1070" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1071" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1072" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1073" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1074" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1075" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1076" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1077" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1078" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1079" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1080" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1081" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1082" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1083" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1084" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1085" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1086" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1087" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1088" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1089" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1090" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1091" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1103" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1104" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1105" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1106" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1107" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1108" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1109" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1110" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1111" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1112" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1113" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1114" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1115" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1116" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1117" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1118" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1119" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1120" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1121" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1122" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1123" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1124" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1125" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1127" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1129" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1131" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1133" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1135" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1137" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1139" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1141" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1143" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1145" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1146" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1147" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1148" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1149" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1092" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1093" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1150" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1151" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13638,562 +14508,562 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="189" t="s">
+      <c r="B1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="189" t="s">
+      <c r="C1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="189" t="s">
+      <c r="D1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="189" t="s">
+      <c r="E1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="189" t="s">
+      <c r="F1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="189" t="s">
+      <c r="G1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="189" t="s">
+      <c r="H1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="189" t="s">
+      <c r="I1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="189" t="s">
+      <c r="J1" s="215" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="189" t="s">
+      <c r="K1" s="215" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="369" t="s">
+      <c r="B2" s="395" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="301" t="s">
+      <c r="C2" s="327" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="328" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="303" t="s">
+      <c r="E2" s="329" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="304" t="s">
+      <c r="F2" s="330" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="305" t="s">
+      <c r="G2" s="331" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="306" t="s">
+      <c r="H2" s="332" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="307" t="s">
+      <c r="I2" s="333" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="308" t="s">
+      <c r="J2" s="334" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="339" t="s">
+      <c r="K2" s="365" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="370" t="s">
+      <c r="B3" s="396" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="320" t="s">
+      <c r="C3" s="346" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="321" t="s">
+      <c r="D3" s="347" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="322" t="s">
+      <c r="E3" s="348" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="323" t="s">
+      <c r="F3" s="349" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="324" t="s">
+      <c r="G3" s="350" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="325" t="s">
+      <c r="H3" s="351" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="326" t="s">
+      <c r="I3" s="352" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="327" t="s">
+      <c r="J3" s="353" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="340" t="s">
+      <c r="K3" s="366" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="371" t="s">
+      <c r="B4" s="397" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="413" t="s">
+      <c r="C4" s="439" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="414" t="s">
+      <c r="D4" s="440" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="415" t="s">
+      <c r="E4" s="441" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="416" t="s">
+      <c r="F4" s="442" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="417" t="s">
+      <c r="G4" s="443" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="418" t="s">
+      <c r="H4" s="444" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="419" t="s">
+      <c r="I4" s="445" t="s">
         <v>71</v>
       </c>
-      <c r="J4" s="420" t="s">
+      <c r="J4" s="446" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="421" t="s">
+      <c r="K4" s="447" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="372" t="s">
+      <c r="B5" s="398" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="422" t="s">
+      <c r="C5" s="448" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="423" t="s">
+      <c r="D5" s="449" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="424" t="s">
+      <c r="E5" s="450" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="425" t="s">
+      <c r="F5" s="451" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="426" t="s">
+      <c r="G5" s="452" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="427" t="s">
+      <c r="H5" s="453" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="428" t="s">
+      <c r="I5" s="454" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="429" t="s">
+      <c r="J5" s="455" t="s">
         <v>81</v>
       </c>
-      <c r="K5" s="430" t="s">
+      <c r="K5" s="456" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="373" t="s">
+      <c r="B6" s="399" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="431" t="s">
+      <c r="C6" s="457" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="432" t="s">
+      <c r="D6" s="458" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="433" t="s">
+      <c r="E6" s="459" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="434" t="s">
+      <c r="F6" s="460" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="435" t="s">
+      <c r="G6" s="461" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="436" t="s">
+      <c r="H6" s="462" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="437" t="s">
+      <c r="I6" s="463" t="s">
         <v>73</v>
       </c>
-      <c r="J6" s="438" t="s">
+      <c r="J6" s="464" t="s">
         <v>82</v>
       </c>
-      <c r="K6" s="439" t="s">
+      <c r="K6" s="465" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="79" t="s">
+      <c r="A7" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="374" t="s">
+      <c r="B7" s="400" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="440" t="s">
+      <c r="C7" s="466" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="441" t="s">
+      <c r="D7" s="467" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="442" t="s">
+      <c r="E7" s="468" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="443" t="s">
+      <c r="F7" s="469" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="444" t="s">
+      <c r="G7" s="470" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="445" t="s">
+      <c r="H7" s="471" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="446" t="s">
+      <c r="I7" s="472" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="447" t="s">
+      <c r="J7" s="473" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="448" t="s">
+      <c r="K7" s="474" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="375" t="s">
+      <c r="B8" s="401" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="449" t="s">
+      <c r="C8" s="475" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="450" t="s">
+      <c r="D8" s="476" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="451" t="s">
+      <c r="E8" s="477" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="452" t="s">
+      <c r="F8" s="478" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="453" t="s">
+      <c r="G8" s="479" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="454" t="s">
+      <c r="H8" s="480" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="455" t="s">
+      <c r="I8" s="481" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="456" t="s">
+      <c r="J8" s="482" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="457" t="s">
+      <c r="K8" s="483" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="376" t="s">
+      <c r="B9" s="402" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="458" t="s">
+      <c r="C9" s="484" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="459" t="s">
+      <c r="D9" s="485" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="460" t="s">
+      <c r="E9" s="486" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="461" t="s">
+      <c r="F9" s="487" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="462" t="s">
+      <c r="G9" s="488" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="463" t="s">
+      <c r="H9" s="489" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="464" t="s">
+      <c r="I9" s="490" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="465" t="s">
+      <c r="J9" s="491" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="466" t="s">
+      <c r="K9" s="492" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="112" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="377" t="s">
+      <c r="B10" s="403" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="467" t="s">
+      <c r="C10" s="493" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="468" t="s">
+      <c r="D10" s="494" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="469" t="s">
+      <c r="E10" s="495" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="470" t="s">
+      <c r="F10" s="496" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="471" t="s">
+      <c r="G10" s="497" t="s">
         <v>62</v>
       </c>
-      <c r="H10" s="472" t="s">
+      <c r="H10" s="498" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="473" t="s">
+      <c r="I10" s="499" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="474" t="s">
+      <c r="J10" s="500" t="s">
         <v>85</v>
       </c>
-      <c r="K10" s="475" t="s">
+      <c r="K10" s="501" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="123" t="s">
+      <c r="A11" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="378" t="s">
+      <c r="B11" s="404" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="476" t="s">
+      <c r="C11" s="502" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="477" t="s">
+      <c r="D11" s="503" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="478" t="s">
+      <c r="E11" s="504" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="479" t="s">
+      <c r="F11" s="505" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="480" t="s">
+      <c r="G11" s="506" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="481" t="s">
+      <c r="H11" s="507" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="482" t="s">
+      <c r="I11" s="508" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="483" t="s">
+      <c r="J11" s="509" t="s">
         <v>63</v>
       </c>
-      <c r="K11" s="484" t="s">
+      <c r="K11" s="510" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="134" t="s">
+      <c r="A12" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="379" t="s">
+      <c r="B12" s="405" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="485" t="s">
+      <c r="C12" s="511" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="486" t="s">
+      <c r="D12" s="512" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="487" t="s">
+      <c r="E12" s="513" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="488" t="s">
+      <c r="F12" s="514" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="489" t="s">
+      <c r="G12" s="515" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="490" t="s">
+      <c r="H12" s="516" t="s">
         <v>69</v>
       </c>
-      <c r="I12" s="491" t="s">
+      <c r="I12" s="517" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="492" t="s">
+      <c r="J12" s="518" t="s">
         <v>86</v>
       </c>
-      <c r="K12" s="493" t="s">
+      <c r="K12" s="519" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="145" t="s">
+      <c r="A13" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="380" t="s">
+      <c r="B13" s="406" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="494" t="s">
+      <c r="C13" s="520" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="495" t="s">
+      <c r="D13" s="521" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="496" t="s">
+      <c r="E13" s="522" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="497" t="s">
+      <c r="F13" s="523" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="498" t="s">
+      <c r="G13" s="524" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="499" t="s">
+      <c r="H13" s="525" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="500" t="s">
+      <c r="I13" s="526" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="501" t="s">
+      <c r="J13" s="527" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="502" t="s">
+      <c r="K13" s="528" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="156" t="s">
+      <c r="A14" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="381" t="s">
+      <c r="B14" s="407" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="503" t="s">
+      <c r="C14" s="529" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="504" t="s">
+      <c r="D14" s="530" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="505" t="s">
+      <c r="E14" s="531" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="506" t="s">
+      <c r="F14" s="532" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="507" t="s">
+      <c r="G14" s="533" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="508" t="s">
+      <c r="H14" s="534" t="s">
         <v>1</v>
       </c>
-      <c r="I14" s="509" t="s">
+      <c r="I14" s="535" t="s">
         <v>78</v>
       </c>
-      <c r="J14" s="510" t="s">
+      <c r="J14" s="536" t="s">
         <v>87</v>
       </c>
-      <c r="K14" s="511" t="s">
+      <c r="K14" s="537" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="167" t="s">
+      <c r="A15" s="193" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="382" t="s">
+      <c r="B15" s="408" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="512" t="s">
+      <c r="C15" s="538" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="513" t="s">
+      <c r="D15" s="539" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="514" t="s">
+      <c r="E15" s="540" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="515" t="s">
+      <c r="F15" s="541" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="516" t="s">
+      <c r="G15" s="542" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="517" t="s">
+      <c r="H15" s="543" t="s">
         <v>42</v>
       </c>
-      <c r="I15" s="518" t="s">
+      <c r="I15" s="544" t="s">
         <v>79</v>
       </c>
-      <c r="J15" s="519" t="s">
+      <c r="J15" s="545" t="s">
         <v>88</v>
       </c>
-      <c r="K15" s="520" t="s">
+      <c r="K15" s="546" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="178" t="s">
+      <c r="A16" s="204" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="394" t="s">
+      <c r="B16" s="420" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="521" t="s">
+      <c r="C16" s="547" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="522" t="s">
+      <c r="D16" s="548" t="s">
         <v>1</v>
       </c>
-      <c r="E16" s="523" t="s">
+      <c r="E16" s="549" t="s">
         <v>1</v>
       </c>
-      <c r="F16" s="524" t="s">
+      <c r="F16" s="550" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="525" t="s">
+      <c r="G16" s="551" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="526" t="s">
+      <c r="H16" s="552" t="s">
         <v>1</v>
       </c>
-      <c r="I16" s="527" t="s">
+      <c r="I16" s="553" t="s">
         <v>27</v>
       </c>
-      <c r="J16" s="528" t="s">
+      <c r="J16" s="554" t="s">
         <v>1</v>
       </c>
-      <c r="K16" s="529" t="s">
+      <c r="K16" s="555" t="s">
         <v>1</v>
       </c>
     </row>
@@ -14215,333 +15085,333 @@
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="531" customWidth="true"/>
-    <col min="2" max="2" width="36.7109375" style="532" customWidth="true"/>
-    <col min="3" max="3" width="7.7109375" style="533" customWidth="true"/>
-    <col min="4" max="4" width="14.2109375" style="534" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="535" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="557" customWidth="true"/>
+    <col min="2" max="2" width="36.7109375" style="558" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="559" customWidth="true"/>
+    <col min="4" max="4" width="14.2109375" style="560" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="561" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="530" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="639" t="s">
+    <row r="1" s="556" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="697" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="631" t="s">
+      <c r="B1" s="689" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="631" t="s">
+      <c r="C1" s="689" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="631" t="s">
+      <c r="D1" s="689" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="631" t="s">
+      <c r="E1" s="689" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="541" t="s">
+      <c r="A2" s="599" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="728" t="s">
+      <c r="B2" s="786" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="678" t="s">
+      <c r="C2" s="736" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="679" t="s">
+      <c r="D2" s="737" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="692" t="s">
+      <c r="E2" s="750" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="546" t="s">
+      <c r="A3" s="604" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="729" t="s">
+      <c r="B3" s="787" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="685" t="s">
+      <c r="C3" s="743" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="686" t="s">
+      <c r="D3" s="744" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="693" t="s">
+      <c r="E3" s="751" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="551" t="s">
+      <c r="A4" s="609" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="730" t="s">
+      <c r="B4" s="788" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="757" t="s">
+      <c r="C4" s="815" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="758" t="s">
+      <c r="D4" s="816" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="759" t="s">
+      <c r="E4" s="817" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="556" t="s">
+      <c r="A5" s="614" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="731" t="s">
+      <c r="B5" s="789" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="760" t="s">
+      <c r="C5" s="818" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="761" t="s">
+      <c r="D5" s="819" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="762" t="s">
+      <c r="E5" s="820" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="561" t="s">
+      <c r="A6" s="619" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="732" t="s">
+      <c r="B6" s="790" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="763" t="s">
+      <c r="C6" s="821" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="764" t="s">
+      <c r="D6" s="822" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="765" t="s">
+      <c r="E6" s="823" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="566" t="s">
+      <c r="A7" s="624" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="733" t="s">
+      <c r="B7" s="791" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="766" t="s">
+      <c r="C7" s="824" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="767" t="s">
+      <c r="D7" s="825" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="768" t="s">
+      <c r="E7" s="826" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="571" t="s">
+      <c r="A8" s="629" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="734" t="s">
+      <c r="B8" s="792" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="769" t="s">
+      <c r="C8" s="827" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="770" t="s">
+      <c r="D8" s="828" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="771" t="s">
+      <c r="E8" s="829" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="576" t="s">
+      <c r="A9" s="634" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="735" t="s">
+      <c r="B9" s="793" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="772" t="s">
+      <c r="C9" s="830" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="773" t="s">
+      <c r="D9" s="831" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="774" t="s">
+      <c r="E9" s="832" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="581" t="s">
+      <c r="A10" s="639" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="736" t="s">
+      <c r="B10" s="794" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="775" t="s">
+      <c r="C10" s="833" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="776" t="s">
+      <c r="D10" s="834" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="777" t="s">
+      <c r="E10" s="835" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="586" t="s">
+      <c r="A11" s="644" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="737" t="s">
+      <c r="B11" s="795" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="778" t="s">
+      <c r="C11" s="836" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="779" t="s">
+      <c r="D11" s="837" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="780" t="s">
+      <c r="E11" s="838" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="591" t="s">
+      <c r="A12" s="649" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="738" t="s">
+      <c r="B12" s="796" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="781" t="s">
+      <c r="C12" s="839" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="782" t="s">
+      <c r="D12" s="840" t="s">
         <v>122</v>
       </c>
-      <c r="E12" s="783" t="s">
+      <c r="E12" s="841" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="596" t="s">
+      <c r="A13" s="654" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="739" t="s">
+      <c r="B13" s="797" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="784" t="s">
+      <c r="C13" s="842" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="785" t="s">
+      <c r="D13" s="843" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="786" t="s">
+      <c r="E13" s="844" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="601" t="s">
+      <c r="A14" s="659" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="740" t="s">
+      <c r="B14" s="798" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="787" t="s">
+      <c r="C14" s="845" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="788" t="s">
+      <c r="D14" s="846" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="789" t="s">
+      <c r="E14" s="847" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="606" t="s">
+      <c r="A15" s="664" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="741" t="s">
+      <c r="B15" s="799" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="790" t="s">
+      <c r="C15" s="848" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="791" t="s">
+      <c r="D15" s="849" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="792" t="s">
+      <c r="E15" s="850" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="611" t="s">
+      <c r="A16" s="669" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="742" t="s">
+      <c r="B16" s="800" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="793" t="s">
+      <c r="C16" s="851" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="794" t="s">
+      <c r="D16" s="852" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="795" t="s">
+      <c r="E16" s="853" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="616" t="s">
+      <c r="A17" s="674" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="743" t="s">
+      <c r="B17" s="801" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="796" t="s">
+      <c r="C17" s="854" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="797" t="s">
+      <c r="D17" s="855" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="798" t="s">
+      <c r="E17" s="856" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="621" t="s">
+      <c r="A18" s="679" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="744" t="s">
+      <c r="B18" s="802" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="799" t="s">
+      <c r="C18" s="857" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="800" t="s">
+      <c r="D18" s="858" t="s">
         <v>128</v>
       </c>
-      <c r="E18" s="801" t="s">
+      <c r="E18" s="859" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="626" t="s">
+      <c r="A19" s="684" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="750" t="s">
+      <c r="B19" s="808" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="802" t="s">
+      <c r="C19" s="860" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="803" t="s">
+      <c r="D19" s="861" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="804" t="s">
+      <c r="E19" s="862" t="s">
         <v>1</v>
       </c>
     </row>

--- a/iivw/demo/iivw_results.xlsx
+++ b/iivw/demo/iivw_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="271" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="271" uniqueCount="134">
   <si>
     <t>IIVW diagnostic model comparison</t>
   </si>
@@ -160,151 +160,136 @@
     <t>FIPTIW</t>
   </si>
   <si>
-    <t>0.23</t>
+    <t>0.28</t>
   </si>
   <si>
-    <t>0.66</t>
+    <t>0.75</t>
   </si>
   <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>-0.22</t>
+    <t>-0.23</t>
   </si>
   <si>
     <t>-0.10</t>
   </si>
   <si>
-    <t>-0.38</t>
+    <t>-0.39</t>
+  </si>
+  <si>
+    <t>3.57</t>
+  </si>
+  <si>
+    <t>(-0.13, 0.68)</t>
+  </si>
+  <si>
+    <t>(0.51, 0.98)</t>
+  </si>
+  <si>
+    <t>(-0.51, 0.05)</t>
+  </si>
+  <si>
+    <t>(-0.34, 0.13)</t>
+  </si>
+  <si>
+    <t>(-0.51, -0.27)</t>
+  </si>
+  <si>
+    <t>(-0.12, 0.34)</t>
+  </si>
+  <si>
+    <t>(2.18, 4.96)</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>FIPTIW + log(test+1)</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>-0.21</t>
+  </si>
+  <si>
+    <t>-0.08</t>
+  </si>
+  <si>
+    <t>-0.29</t>
+  </si>
+  <si>
+    <t>2.98</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>(-0.30, 0.49)</t>
+  </si>
+  <si>
+    <t>(-0.82, 0.05)</t>
+  </si>
+  <si>
+    <t>(0.00, 0.59)</t>
+  </si>
+  <si>
+    <t>(-0.49, 0.07)</t>
+  </si>
+  <si>
+    <t>(-0.03, 0.00)</t>
+  </si>
+  <si>
+    <t>(-0.30, 0.15)</t>
+  </si>
+  <si>
+    <t>(-0.42, -0.16)</t>
+  </si>
+  <si>
+    <t>(-0.04, 0.03)</t>
+  </si>
+  <si>
+    <t>(-0.11, 0.33)</t>
+  </si>
+  <si>
+    <t>(1.85, 4.11)</t>
+  </si>
+  <si>
+    <t>(-0.57, 2.80)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>0.050</t>
   </si>
   <si>
     <t>0.13</t>
   </si>
   <si>
-    <t>3.75</t>
-  </si>
-  <si>
-    <t>(-0.18, 0.65)</t>
-  </si>
-  <si>
-    <t>(0.49, 0.82)</t>
-  </si>
-  <si>
-    <t>(0.53, 0.99)</t>
-  </si>
-  <si>
-    <t>(-0.50, 0.06)</t>
-  </si>
-  <si>
-    <t>(-0.03, 0.00)</t>
-  </si>
-  <si>
-    <t>(-0.34, 0.13)</t>
-  </si>
-  <si>
-    <t>(-0.50, -0.25)</t>
-  </si>
-  <si>
-    <t>(-0.04, 0.03)</t>
-  </si>
-  <si>
-    <t>(-0.11, 0.36)</t>
-  </si>
-  <si>
-    <t>(2.30, 5.20)</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>FIPTIW + log(test+1)</t>
-  </si>
-  <si>
-    <t>0.02</t>
-  </si>
-  <si>
-    <t>-0.48</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>-0.20</t>
-  </si>
-  <si>
-    <t>-0.02</t>
-  </si>
-  <si>
-    <t>-0.08</t>
-  </si>
-  <si>
-    <t>-0.27</t>
-  </si>
-  <si>
-    <t>3.16</t>
-  </si>
-  <si>
-    <t>1.07</t>
-  </si>
-  <si>
-    <t>(-0.39, 0.43)</t>
-  </si>
-  <si>
-    <t>(-0.92, -0.05)</t>
-  </si>
-  <si>
-    <t>(0.00, 0.59)</t>
-  </si>
-  <si>
-    <t>(-0.48, 0.08)</t>
-  </si>
-  <si>
-    <t>(-0.31, 0.15)</t>
-  </si>
-  <si>
-    <t>(-0.41, -0.14)</t>
-  </si>
-  <si>
-    <t>(-0.10, 0.35)</t>
-  </si>
-  <si>
-    <t>(2.02, 4.30)</t>
-  </si>
-  <si>
-    <t>(-0.70, 2.84)</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>0.17</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
     <t>0.51</t>
   </si>
   <si>
-    <t>0.69</t>
+    <t>0.33</t>
   </si>
   <si>
-    <t>0.24</t>
+    <t>0.20</t>
   </si>
   <si>
     <t>Treatment by visit wave</t>
@@ -337,28 +322,34 @@
     <t>0.37</t>
   </si>
   <si>
-    <t>-0.03</t>
+    <t>-0.04</t>
   </si>
   <si>
-    <t>0.03</t>
+    <t>-0.20</t>
   </si>
   <si>
-    <t>1.03</t>
+    <t>-0.02</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>1.02</t>
   </si>
   <si>
     <t>1.56</t>
   </si>
   <si>
-    <t>2.12</t>
-  </si>
-  <si>
-    <t>-0.12</t>
+    <t>2.13</t>
   </si>
   <si>
     <t>-0.09</t>
   </si>
   <si>
-    <t>2.91</t>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>2.90</t>
   </si>
   <si>
     <t>1,243</t>
@@ -367,7 +358,7 @@
     <t>(-0.17, 0.91)</t>
   </si>
   <si>
-    <t>(-0.31, 0.25)</t>
+    <t>(-0.32, 0.24)</t>
   </si>
   <si>
     <t>(-0.35, -0.05)</t>
@@ -376,58 +367,55 @@
     <t>(-0.06, 0.03)</t>
   </si>
   <si>
-    <t>(-0.25, 0.32)</t>
+    <t>(-0.24, 0.32)</t>
   </si>
   <si>
     <t>(-0.47, 0.24)</t>
   </si>
   <si>
-    <t>(0.49, 1.56)</t>
+    <t>(0.49, 1.55)</t>
   </si>
   <si>
     <t>(1.02, 2.11)</t>
   </si>
   <si>
-    <t>(1.58, 2.66)</t>
+    <t>(1.59, 2.67)</t>
   </si>
   <si>
-    <t>(-0.88, 0.64)</t>
+    <t>(-0.87, 0.65)</t>
   </si>
   <si>
-    <t>(-0.81, 0.63)</t>
+    <t>(-0.81, 0.64)</t>
   </si>
   <si>
-    <t>(-0.39, 1.12)</t>
+    <t>(-0.40, 1.11)</t>
   </si>
   <si>
-    <t>(1.29, 4.53)</t>
-  </si>
-  <si>
-    <t>0.18</t>
+    <t>(1.29, 4.51)</t>
   </si>
   <si>
     <t>0.26</t>
   </si>
   <si>
-    <t>0.84</t>
+    <t>0.80</t>
   </si>
   <si>
-    <t>0.010</t>
+    <t>0.011</t>
   </si>
   <si>
-    <t>0.49</t>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>0.53</t>
   </si>
   <si>
     <t>0.81</t>
   </si>
   <si>
-    <t>0.53</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>0.34</t>
+    <t>0.35</t>
   </si>
 </sst>
 </file>
@@ -14568,7 +14556,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="333" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J2" s="334" t="s">
         <v>1</v>
@@ -14632,19 +14620,19 @@
         <v>48</v>
       </c>
       <c r="G4" s="443" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H4" s="444" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I4" s="445" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J4" s="446" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K4" s="447" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -14664,22 +14652,22 @@
         <v>42</v>
       </c>
       <c r="F5" s="451" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G5" s="452" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H5" s="453" t="s">
         <v>42</v>
       </c>
       <c r="I5" s="454" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="J5" s="455" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K5" s="456" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6">
@@ -14699,22 +14687,22 @@
         <v>42</v>
       </c>
       <c r="F6" s="460" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" s="461" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H6" s="462" t="s">
         <v>42</v>
       </c>
       <c r="I6" s="463" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="J6" s="464" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K6" s="465" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -14734,22 +14722,22 @@
         <v>43</v>
       </c>
       <c r="F7" s="469" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="470" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H7" s="471" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="I7" s="472" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J7" s="473" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K7" s="474" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
@@ -14772,19 +14760,19 @@
         <v>21</v>
       </c>
       <c r="G8" s="479" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="H8" s="480" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="I8" s="481" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="J8" s="482" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K8" s="483" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -14804,22 +14792,22 @@
         <v>17</v>
       </c>
       <c r="F9" s="487" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="488" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H9" s="489" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I9" s="490" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J9" s="491" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K9" s="492" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -14839,19 +14827,19 @@
         <v>42</v>
       </c>
       <c r="F10" s="496" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" s="497" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H10" s="498" t="s">
         <v>42</v>
       </c>
       <c r="I10" s="499" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J10" s="500" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K10" s="501" t="s">
         <v>42</v>
@@ -14877,19 +14865,19 @@
         <v>21</v>
       </c>
       <c r="G11" s="506" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="H11" s="507" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I11" s="508" t="s">
         <v>21</v>
       </c>
       <c r="J11" s="509" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="K11" s="510" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -14909,22 +14897,22 @@
         <v>46</v>
       </c>
       <c r="F12" s="514" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G12" s="515" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H12" s="516" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I12" s="517" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="J12" s="518" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K12" s="519" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -14988,10 +14976,10 @@
         <v>1</v>
       </c>
       <c r="I14" s="535" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J14" s="536" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K14" s="537" t="s">
         <v>42</v>
@@ -15014,22 +15002,22 @@
         <v>42</v>
       </c>
       <c r="F15" s="541" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G15" s="542" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H15" s="543" t="s">
         <v>42</v>
       </c>
       <c r="I15" s="544" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J15" s="545" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K15" s="546" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -15094,7 +15082,7 @@
   <sheetData>
     <row r="1" s="556" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="697" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B1" s="689" t="s">
         <v>1</v>
@@ -15117,7 +15105,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="736" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D2" s="737" t="s">
         <v>1</v>
@@ -15148,16 +15136,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="788" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C4" s="815" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D4" s="816" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E4" s="817" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -15174,7 +15162,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="820" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
@@ -15185,13 +15173,13 @@
         <v>7</v>
       </c>
       <c r="C6" s="821" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D6" s="822" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E6" s="823" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
@@ -15202,13 +15190,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="824" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D7" s="825" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E7" s="826" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8">
@@ -15219,13 +15207,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="827" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="D8" s="828" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E8" s="829" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
@@ -15236,13 +15224,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="830" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D9" s="831" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E9" s="832" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -15273,10 +15261,10 @@
         <v>22</v>
       </c>
       <c r="D11" s="837" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E11" s="838" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -15284,13 +15272,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="796" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C12" s="839" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" s="840" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E12" s="841" t="s">
         <v>42</v>
@@ -15301,13 +15289,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="797" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C13" s="842" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D13" s="843" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E13" s="844" t="s">
         <v>42</v>
@@ -15318,13 +15306,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="798" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C14" s="845" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D14" s="846" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E14" s="847" t="s">
         <v>42</v>
@@ -15335,16 +15323,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="799" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C15" s="848" t="s">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="D15" s="849" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E15" s="850" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
@@ -15352,16 +15340,16 @@
         <v>1</v>
       </c>
       <c r="B16" s="800" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C16" s="851" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D16" s="852" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E16" s="853" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -15369,16 +15357,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="801" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C17" s="854" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D17" s="855" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E17" s="856" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
@@ -15389,10 +15377,10 @@
         <v>13</v>
       </c>
       <c r="C18" s="857" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D18" s="858" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E18" s="859" t="s">
         <v>42</v>
@@ -15406,7 +15394,7 @@
         <v>14</v>
       </c>
       <c r="C19" s="860" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D19" s="861" t="s">
         <v>1</v>

--- a/iivw/demo/iivw_results.xlsx
+++ b/iivw/demo/iivw_results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="271" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="271" uniqueCount="140">
   <si>
     <t>IIVW diagnostic model comparison</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Unweighted</t>
   </si>
   <si>
-    <t>Coef.</t>
+    <t>_r_b</t>
   </si>
   <si>
     <t>0.32</t>
@@ -163,10 +163,10 @@
     <t>0.28</t>
   </si>
   <si>
-    <t>0.75</t>
+    <t>0.74</t>
   </si>
   <si>
-    <t>-0.23</t>
+    <t>-0.24</t>
   </si>
   <si>
     <t>-0.10</t>
@@ -175,79 +175,85 @@
     <t>-0.39</t>
   </si>
   <si>
-    <t>3.57</t>
+    <t>3.53</t>
   </si>
   <si>
-    <t>(-0.13, 0.68)</t>
+    <t>(-0.12, 0.69)</t>
+  </si>
+  <si>
+    <t>(0.57, 0.90)</t>
   </si>
   <si>
     <t>(0.51, 0.98)</t>
   </si>
   <si>
-    <t>(-0.51, 0.05)</t>
+    <t>(-0.52, 0.04)</t>
   </si>
   <si>
     <t>(-0.34, 0.13)</t>
   </si>
   <si>
-    <t>(-0.51, -0.27)</t>
+    <t>(-0.51, -0.26)</t>
   </si>
   <si>
     <t>(-0.12, 0.34)</t>
   </si>
   <si>
-    <t>(2.18, 4.96)</t>
+    <t>(2.14, 4.91)</t>
   </si>
   <si>
-    <t>0.18</t>
+    <t>0.17</t>
   </si>
   <si>
-    <t>0.21</t>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>0.24</t>
   </si>
   <si>
     <t>0.38</t>
   </si>
   <si>
-    <t>0.59</t>
+    <t>0.58</t>
   </si>
   <si>
-    <t>0.34</t>
+    <t>0.36</t>
   </si>
   <si>
     <t>FIPTIW + log(test+1)</t>
   </si>
   <si>
-    <t>0.09</t>
+    <t>-0.38</t>
   </si>
   <si>
-    <t>0.30</t>
+    <t>0.29</t>
   </si>
   <si>
-    <t>-0.21</t>
+    <t>-0.22</t>
   </si>
   <si>
     <t>-0.08</t>
   </si>
   <si>
-    <t>-0.29</t>
+    <t>-0.28</t>
   </si>
   <si>
-    <t>2.98</t>
+    <t>2.96</t>
   </si>
   <si>
-    <t>1.12</t>
+    <t>1.10</t>
   </si>
   <si>
-    <t>(-0.30, 0.49)</t>
+    <t>(-0.29, 0.50)</t>
   </si>
   <si>
-    <t>(-0.82, 0.05)</t>
+    <t>(-0.82, 0.06)</t>
   </si>
   <si>
-    <t>(0.00, 0.59)</t>
+    <t>(-0.00, 0.59)</t>
   </si>
   <si>
-    <t>(-0.49, 0.07)</t>
+    <t>(-0.50, 0.06)</t>
   </si>
   <si>
     <t>(-0.03, 0.00)</t>
@@ -256,37 +262,43 @@
     <t>(-0.30, 0.15)</t>
   </si>
   <si>
-    <t>(-0.42, -0.16)</t>
+    <t>(-0.42, -0.15)</t>
   </si>
   <si>
     <t>(-0.04, 0.03)</t>
   </si>
   <si>
-    <t>(-0.11, 0.33)</t>
+    <t>(-0.12, 0.33)</t>
   </si>
   <si>
-    <t>(1.85, 4.11)</t>
+    <t>(1.83, 4.10)</t>
   </si>
   <si>
-    <t>(-0.57, 2.80)</t>
+    <t>(-0.58, 2.77)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>0.51</t>
   </si>
   <si>
     <t>0.65</t>
   </si>
   <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>0.33</t>
+    <t>0.34</t>
   </si>
   <si>
     <t>0.20</t>
@@ -319,6 +331,9 @@
     <t>Model</t>
   </si>
   <si>
+    <t>Coef.</t>
+  </si>
+  <si>
     <t>0.37</t>
   </si>
   <si>
@@ -334,6 +349,9 @@
     <t>0.04</t>
   </si>
   <si>
+    <t>-0.12</t>
+  </si>
+  <si>
     <t>1.02</t>
   </si>
   <si>
@@ -346,10 +364,7 @@
     <t>-0.09</t>
   </si>
   <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>2.90</t>
+    <t>2.89</t>
   </si>
   <si>
     <t>1,243</t>
@@ -391,10 +406,13 @@
     <t>(-0.40, 1.11)</t>
   </si>
   <si>
-    <t>(1.29, 4.51)</t>
+    <t>(1.28, 4.50)</t>
   </si>
   <si>
-    <t>0.26</t>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>0.27</t>
   </si>
   <si>
     <t>0.80</t>
@@ -409,7 +427,7 @@
     <t>0.77</t>
   </si>
   <si>
-    <t>0.53</t>
+    <t>0.52</t>
   </si>
   <si>
     <t>0.81</t>
@@ -14556,7 +14574,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="333" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J2" s="334" t="s">
         <v>1</v>
@@ -14623,16 +14641,16 @@
         <v>54</v>
       </c>
       <c r="H4" s="444" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I4" s="445" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="J4" s="446" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="447" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -14655,19 +14673,19 @@
         <v>18</v>
       </c>
       <c r="G5" s="452" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H5" s="453" t="s">
         <v>42</v>
       </c>
       <c r="I5" s="454" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="J5" s="455" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K5" s="456" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -14690,19 +14708,19 @@
         <v>49</v>
       </c>
       <c r="G6" s="461" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="462" t="s">
         <v>42</v>
       </c>
       <c r="I6" s="463" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J6" s="464" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K6" s="465" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -14725,19 +14743,19 @@
         <v>50</v>
       </c>
       <c r="G7" s="470" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" s="471" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="I7" s="472" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J7" s="473" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K7" s="474" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -14763,16 +14781,16 @@
         <v>33</v>
       </c>
       <c r="H8" s="480" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I8" s="481" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="482" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K8" s="483" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -14795,19 +14813,19 @@
         <v>51</v>
       </c>
       <c r="G9" s="488" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H9" s="489" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I9" s="490" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J9" s="491" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K9" s="492" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -14830,16 +14848,16 @@
         <v>52</v>
       </c>
       <c r="G10" s="497" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H10" s="498" t="s">
         <v>42</v>
       </c>
       <c r="I10" s="499" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J10" s="500" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K10" s="501" t="s">
         <v>42</v>
@@ -14868,16 +14886,16 @@
         <v>36</v>
       </c>
       <c r="H11" s="507" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I11" s="508" t="s">
         <v>21</v>
       </c>
       <c r="J11" s="509" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K11" s="510" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -14900,19 +14918,19 @@
         <v>41</v>
       </c>
       <c r="G12" s="515" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" s="516" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I12" s="517" t="s">
         <v>41</v>
       </c>
       <c r="J12" s="518" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K12" s="519" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -14976,10 +14994,10 @@
         <v>1</v>
       </c>
       <c r="I14" s="535" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="536" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K14" s="537" t="s">
         <v>42</v>
@@ -15005,19 +15023,19 @@
         <v>53</v>
       </c>
       <c r="G15" s="542" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" s="543" t="s">
         <v>42</v>
       </c>
       <c r="I15" s="544" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J15" s="545" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K15" s="546" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -15082,7 +15100,7 @@
   <sheetData>
     <row r="1" s="556" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="697" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="689" t="s">
         <v>1</v>
@@ -15105,7 +15123,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="736" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D2" s="737" t="s">
         <v>1</v>
@@ -15122,7 +15140,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="743" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="D3" s="744" t="s">
         <v>28</v>
@@ -15136,16 +15154,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="788" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C4" s="815" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D4" s="816" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E4" s="817" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
@@ -15162,7 +15180,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="820" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
@@ -15173,13 +15191,13 @@
         <v>7</v>
       </c>
       <c r="C6" s="821" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D6" s="822" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E6" s="823" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
@@ -15190,13 +15208,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="824" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D7" s="825" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E7" s="826" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
@@ -15207,13 +15225,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="827" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D8" s="828" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E8" s="829" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
@@ -15224,13 +15242,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="830" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D9" s="831" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E9" s="832" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -15258,13 +15276,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="836" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="D11" s="837" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E11" s="838" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -15272,13 +15290,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="796" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C12" s="839" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D12" s="840" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E12" s="841" t="s">
         <v>42</v>
@@ -15289,13 +15307,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="797" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C13" s="842" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D13" s="843" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E13" s="844" t="s">
         <v>42</v>
@@ -15306,13 +15324,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="798" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C14" s="845" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D14" s="846" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E14" s="847" t="s">
         <v>42</v>
@@ -15323,16 +15341,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="799" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C15" s="848" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="849" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E15" s="850" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
@@ -15340,16 +15358,16 @@
         <v>1</v>
       </c>
       <c r="B16" s="800" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C16" s="851" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D16" s="852" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E16" s="853" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -15357,16 +15375,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="801" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C17" s="854" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D17" s="855" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E17" s="856" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
@@ -15377,10 +15395,10 @@
         <v>13</v>
       </c>
       <c r="C18" s="857" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D18" s="858" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E18" s="859" t="s">
         <v>42</v>
@@ -15394,7 +15412,7 @@
         <v>14</v>
       </c>
       <c r="C19" s="860" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D19" s="861" t="s">
         <v>1</v>
